--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,22 +420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4728682170542636</v>
+        <v>0.6875</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4718309859154929</v>
+        <v>0.6619718309859155</v>
       </c>
       <c r="D2">
-        <v>0.5514705882352942</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="E2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2">
         <v>6</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6875</v>
+        <v>0.671875</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6619718309859155</v>
+        <v>0.6549295774647887</v>
       </c>
       <c r="D2">
-        <v>0.3529411764705883</v>
+        <v>0.362962962962963</v>
       </c>
       <c r="E2">
         <v>128</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
